--- a/results/Stage3Candidates_completed.xlsx
+++ b/results/Stage3Candidates_completed.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mhhm1\Documents\ML_Discovery_Metal-Organic_Adsorbents\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hsm24sch\Documents\ML_Discovery_Metal-Organic_Adsobents\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61EF5182-9BC7-49C9-B2A1-63B4C4352B5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09F887B9-A7B3-4400-9AD4-1F1775D44D60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="94">
   <si>
     <t>Dataset</t>
   </si>
@@ -313,13 +314,26 @@
   </si>
   <si>
     <t>NA</t>
+  </si>
+  <si>
+    <t>Energy</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -345,13 +359,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -630,14 +653,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O29"/>
+  <dimension ref="A1:W29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
     <col min="4" max="10" width="0" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -669,19 +693,43 @@
         <v>13</v>
       </c>
       <c r="K1" t="s">
+        <v>93</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S1" t="s">
         <v>14</v>
       </c>
-      <c r="M1" t="s">
+      <c r="U1" t="s">
         <v>89</v>
       </c>
-      <c r="N1" t="s">
+      <c r="V1" t="s">
         <v>90</v>
       </c>
-      <c r="O1" t="s">
+      <c r="W1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -712,21 +760,45 @@
       <c r="J2">
         <v>5.2996699999999999</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2">
+        <v>-5.181</v>
+      </c>
+      <c r="L2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="3">
+        <v>0.175207</v>
+      </c>
+      <c r="O2" s="3">
+        <v>15.583130000000001</v>
+      </c>
+      <c r="P2" s="3">
+        <v>22.94791</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>0.92854000000000003</v>
+      </c>
+      <c r="R2" s="3">
+        <v>5.2996699999999999</v>
+      </c>
+      <c r="S2" t="s">
         <v>15</v>
       </c>
-      <c r="M2">
+      <c r="U2">
         <v>-5.2389999999999999</v>
       </c>
-      <c r="N2">
+      <c r="V2">
         <v>-5.1230000000000002</v>
       </c>
-      <c r="O2">
-        <f>M2+(N2-M2)/2</f>
+      <c r="W2">
+        <f>U2+(V2-U2)/2</f>
         <v>-5.181</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -757,21 +829,45 @@
       <c r="J3">
         <v>3.08066</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3">
+        <v>-11.085000000000001</v>
+      </c>
+      <c r="L3" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N3" s="3">
+        <v>0.284192</v>
+      </c>
+      <c r="O3" s="3">
+        <v>26.589400000000001</v>
+      </c>
+      <c r="P3" s="3">
+        <v>28.055990000000001</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>0.87549999999999994</v>
+      </c>
+      <c r="R3" s="3">
+        <v>3.08066</v>
+      </c>
+      <c r="S3" t="s">
         <v>15</v>
       </c>
-      <c r="M3">
+      <c r="U3">
         <v>-11.11</v>
       </c>
-      <c r="N3">
+      <c r="V3">
         <v>-11.06</v>
       </c>
-      <c r="O3">
-        <f t="shared" ref="O3:O25" si="0">M3+(N3-M3)/2</f>
+      <c r="W3">
+        <f t="shared" ref="W3:W25" si="0">U3+(V3-U3)/2</f>
         <v>-11.085000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -802,21 +898,45 @@
       <c r="J4">
         <v>2.7129599999999998</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4">
+        <v>-9.3509999999999991</v>
+      </c>
+      <c r="L4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N4" s="3">
+        <v>0.31795499999999999</v>
+      </c>
+      <c r="O4" s="3">
+        <v>12.16855</v>
+      </c>
+      <c r="P4" s="3">
+        <v>22.459579999999999</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>0.86260000000000003</v>
+      </c>
+      <c r="R4" s="3">
+        <v>2.7129599999999998</v>
+      </c>
+      <c r="S4" t="s">
         <v>15</v>
       </c>
-      <c r="M4">
+      <c r="U4">
         <v>-9.3559999999999999</v>
       </c>
-      <c r="N4">
+      <c r="V4">
         <v>-9.3460000000000001</v>
       </c>
-      <c r="O4">
+      <c r="W4">
         <f t="shared" si="0"/>
         <v>-9.3509999999999991</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -847,21 +967,45 @@
       <c r="J5">
         <v>0.49152600000000002</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5">
+        <v>-15.66</v>
+      </c>
+      <c r="L5" t="s">
+        <v>24</v>
+      </c>
+      <c r="M5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N5" s="3">
+        <v>1.38141</v>
+      </c>
+      <c r="O5" s="3">
+        <v>11.60045</v>
+      </c>
+      <c r="P5" s="3">
+        <v>12.488670000000001</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>0.67900000000000005</v>
+      </c>
+      <c r="R5" s="3">
+        <v>0.49152600000000002</v>
+      </c>
+      <c r="S5" t="s">
         <v>15</v>
       </c>
-      <c r="M5">
+      <c r="U5">
         <v>-15.86</v>
       </c>
-      <c r="N5">
+      <c r="V5">
         <v>-15.46</v>
       </c>
-      <c r="O5">
+      <c r="W5">
         <f t="shared" si="0"/>
         <v>-15.66</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -892,21 +1036,45 @@
       <c r="J6">
         <v>0.85289599999999999</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6">
+        <v>-16.375</v>
+      </c>
+      <c r="L6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N6" s="3">
+        <v>0.90925500000000004</v>
+      </c>
+      <c r="O6" s="3">
+        <v>14.138949999999999</v>
+      </c>
+      <c r="P6" s="3">
+        <v>15.22231</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>0.77549999999999997</v>
+      </c>
+      <c r="R6" s="3">
+        <v>0.85289599999999999</v>
+      </c>
+      <c r="S6" t="s">
         <v>15</v>
       </c>
-      <c r="M6">
+      <c r="U6">
         <v>-16.41</v>
       </c>
-      <c r="N6">
+      <c r="V6">
         <v>-16.34</v>
       </c>
-      <c r="O6">
+      <c r="W6">
         <f t="shared" si="0"/>
         <v>-16.375</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -937,21 +1105,45 @@
       <c r="J7">
         <v>0.49195499999999998</v>
       </c>
-      <c r="K7" t="s">
+      <c r="K7">
+        <v>-20.259999999999998</v>
+      </c>
+      <c r="L7" t="s">
+        <v>30</v>
+      </c>
+      <c r="M7" t="s">
+        <v>31</v>
+      </c>
+      <c r="N7" s="3">
+        <v>1.2596700000000001</v>
+      </c>
+      <c r="O7" s="3">
+        <v>8.7666900000000005</v>
+      </c>
+      <c r="P7" s="3">
+        <v>9.2239699999999996</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>0.61970000000000003</v>
+      </c>
+      <c r="R7" s="3">
+        <v>0.49195499999999998</v>
+      </c>
+      <c r="S7" t="s">
         <v>15</v>
       </c>
-      <c r="M7">
+      <c r="U7">
         <v>-20.48</v>
       </c>
-      <c r="N7">
+      <c r="V7">
         <v>-20.04</v>
       </c>
-      <c r="O7">
+      <c r="W7">
         <f t="shared" si="0"/>
         <v>-20.259999999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -982,21 +1174,45 @@
       <c r="J8">
         <v>0.80959999999999999</v>
       </c>
-      <c r="K8" t="s">
+      <c r="K8">
+        <v>-18.925000000000001</v>
+      </c>
+      <c r="L8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M8" t="s">
+        <v>34</v>
+      </c>
+      <c r="N8" s="3">
+        <v>0.89958000000000005</v>
+      </c>
+      <c r="O8" s="3">
+        <v>7.2826300000000002</v>
+      </c>
+      <c r="P8" s="3">
+        <v>13.220230000000001</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>0.72829999999999995</v>
+      </c>
+      <c r="R8" s="3">
+        <v>0.80959999999999999</v>
+      </c>
+      <c r="S8" t="s">
         <v>15</v>
       </c>
-      <c r="M8">
+      <c r="U8">
         <v>-18.940000000000001</v>
       </c>
-      <c r="N8">
+      <c r="V8">
         <v>-18.91</v>
       </c>
-      <c r="O8">
+      <c r="W8">
         <f t="shared" si="0"/>
         <v>-18.925000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1027,21 +1243,45 @@
       <c r="J9">
         <v>0.45014199999999999</v>
       </c>
-      <c r="K9" t="s">
+      <c r="K9">
+        <v>-18.824999999999999</v>
+      </c>
+      <c r="L9" t="s">
+        <v>36</v>
+      </c>
+      <c r="M9" t="s">
+        <v>37</v>
+      </c>
+      <c r="N9" s="3">
+        <v>1.56151</v>
+      </c>
+      <c r="O9" s="3">
+        <v>6.1713699999999996</v>
+      </c>
+      <c r="P9" s="3">
+        <v>11.808210000000001</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>0.70289999999999997</v>
+      </c>
+      <c r="R9" s="3">
+        <v>0.45014199999999999</v>
+      </c>
+      <c r="S9" t="s">
         <v>15</v>
       </c>
-      <c r="M9">
+      <c r="U9">
         <v>-18.88</v>
       </c>
-      <c r="N9">
+      <c r="V9">
         <v>-18.77</v>
       </c>
-      <c r="O9">
+      <c r="W9">
         <f t="shared" si="0"/>
         <v>-18.824999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -1072,21 +1312,45 @@
       <c r="J10">
         <v>0.75703500000000001</v>
       </c>
-      <c r="K10" t="s">
+      <c r="K10">
+        <v>-13.245000000000001</v>
+      </c>
+      <c r="L10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M10" t="s">
+        <v>40</v>
+      </c>
+      <c r="N10" s="3">
+        <v>0.88899499999999998</v>
+      </c>
+      <c r="O10" s="3">
+        <v>8.2379499999999997</v>
+      </c>
+      <c r="P10" s="3">
+        <v>9.7940900000000006</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>0.67300000000000004</v>
+      </c>
+      <c r="R10" s="3">
+        <v>0.75703500000000001</v>
+      </c>
+      <c r="S10" t="s">
         <v>15</v>
       </c>
-      <c r="M10">
+      <c r="U10">
         <v>-13.42</v>
       </c>
-      <c r="N10">
+      <c r="V10">
         <v>-13.07</v>
       </c>
-      <c r="O10">
+      <c r="W10">
         <f t="shared" si="0"/>
         <v>-13.245000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -1117,21 +1381,45 @@
       <c r="J11">
         <v>0.850939</v>
       </c>
-      <c r="K11" t="s">
+      <c r="K11">
+        <v>-13.305</v>
+      </c>
+      <c r="L11" t="s">
+        <v>42</v>
+      </c>
+      <c r="M11" t="s">
+        <v>25</v>
+      </c>
+      <c r="N11" s="3">
+        <v>0.833314</v>
+      </c>
+      <c r="O11" s="3">
+        <v>8.5407899999999994</v>
+      </c>
+      <c r="P11" s="3">
+        <v>9.9702599999999997</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>0.70909999999999995</v>
+      </c>
+      <c r="R11" s="3">
+        <v>0.850939</v>
+      </c>
+      <c r="S11" t="s">
         <v>15</v>
       </c>
-      <c r="M11">
+      <c r="U11">
         <v>-13.38</v>
       </c>
-      <c r="N11">
+      <c r="V11">
         <v>-13.23</v>
       </c>
-      <c r="O11">
+      <c r="W11">
         <f t="shared" si="0"/>
         <v>-13.305</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -1162,21 +1450,45 @@
       <c r="J12">
         <v>1.0171300000000001</v>
       </c>
-      <c r="K12" t="s">
+      <c r="K12">
+        <v>-9.3375000000000004</v>
+      </c>
+      <c r="L12" t="s">
+        <v>44</v>
+      </c>
+      <c r="M12" t="s">
+        <v>45</v>
+      </c>
+      <c r="N12" s="3">
+        <v>0.70806999999999998</v>
+      </c>
+      <c r="O12" s="3">
+        <v>9.5747199999999992</v>
+      </c>
+      <c r="P12" s="3">
+        <v>12.54203</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>0.72019999999999995</v>
+      </c>
+      <c r="R12" s="3">
+        <v>1.0171300000000001</v>
+      </c>
+      <c r="S12" t="s">
         <v>15</v>
       </c>
-      <c r="M12">
+      <c r="U12">
         <v>-9.4390000000000001</v>
       </c>
-      <c r="N12">
+      <c r="V12">
         <v>-9.2360000000000007</v>
       </c>
-      <c r="O12">
+      <c r="W12">
         <f t="shared" si="0"/>
         <v>-9.3375000000000004</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -1207,21 +1519,45 @@
       <c r="J13">
         <v>1.0342100000000001</v>
       </c>
-      <c r="K13" t="s">
+      <c r="K13">
+        <v>-13.125</v>
+      </c>
+      <c r="L13" t="s">
+        <v>47</v>
+      </c>
+      <c r="M13" t="s">
+        <v>48</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0.70865800000000001</v>
+      </c>
+      <c r="O13" s="3">
+        <v>6.1979199999999999</v>
+      </c>
+      <c r="P13" s="3">
+        <v>11.543760000000001</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0.7329</v>
+      </c>
+      <c r="R13" s="3">
+        <v>1.0342100000000001</v>
+      </c>
+      <c r="S13" t="s">
         <v>15</v>
       </c>
-      <c r="M13">
+      <c r="U13">
         <v>-13.15</v>
       </c>
-      <c r="N13">
+      <c r="V13">
         <v>-13.1</v>
       </c>
-      <c r="O13">
+      <c r="W13">
         <f t="shared" si="0"/>
         <v>-13.125</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -1252,21 +1588,45 @@
       <c r="J14">
         <v>1.13567</v>
       </c>
-      <c r="K14" t="s">
+      <c r="K14">
+        <v>-16.195</v>
+      </c>
+      <c r="L14" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" t="s">
+        <v>51</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0.63210100000000002</v>
+      </c>
+      <c r="O14" s="3">
+        <v>6.5133400000000004</v>
+      </c>
+      <c r="P14" s="3">
+        <v>10.863440000000001</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0.71786000000000005</v>
+      </c>
+      <c r="R14" s="3">
+        <v>1.13567</v>
+      </c>
+      <c r="S14" t="s">
         <v>15</v>
       </c>
-      <c r="M14">
+      <c r="U14">
         <v>-16.23</v>
       </c>
-      <c r="N14">
+      <c r="V14">
         <v>-16.16</v>
       </c>
-      <c r="O14">
+      <c r="W14">
         <f t="shared" si="0"/>
         <v>-16.195</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -1297,21 +1657,45 @@
       <c r="J15">
         <v>0.86689099999999997</v>
       </c>
-      <c r="K15" t="s">
+      <c r="K15">
+        <v>-14.234999999999999</v>
+      </c>
+      <c r="L15" t="s">
+        <v>53</v>
+      </c>
+      <c r="M15" t="s">
+        <v>54</v>
+      </c>
+      <c r="N15" s="3">
+        <v>0.76535500000000001</v>
+      </c>
+      <c r="O15" s="3">
+        <v>10.29832</v>
+      </c>
+      <c r="P15" s="3">
+        <v>10.43276</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0.66347999999999996</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0.86689099999999997</v>
+      </c>
+      <c r="S15" t="s">
         <v>15</v>
       </c>
-      <c r="M15">
+      <c r="U15">
         <v>-14.36</v>
       </c>
-      <c r="N15">
+      <c r="V15">
         <v>-14.11</v>
       </c>
-      <c r="O15">
+      <c r="W15">
         <f t="shared" si="0"/>
         <v>-14.234999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -1342,21 +1726,45 @@
       <c r="J16">
         <v>1.14506</v>
       </c>
-      <c r="K16" t="s">
+      <c r="K16">
+        <v>-14.620000000000001</v>
+      </c>
+      <c r="L16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N16" s="3">
+        <v>0.64188900000000004</v>
+      </c>
+      <c r="O16" s="3">
+        <v>4.1592000000000002</v>
+      </c>
+      <c r="P16" s="3">
+        <v>9.4749199999999991</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>0.73499999999999999</v>
+      </c>
+      <c r="R16" s="3">
+        <v>1.14506</v>
+      </c>
+      <c r="S16" t="s">
         <v>15</v>
       </c>
-      <c r="M16">
+      <c r="U16">
         <v>-14.65</v>
       </c>
-      <c r="N16">
+      <c r="V16">
         <v>-14.59</v>
       </c>
-      <c r="O16">
-        <f>M16+(N16-M16)/2</f>
+      <c r="W16">
+        <f>U16+(V16-U16)/2</f>
         <v>-14.620000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -1387,21 +1795,45 @@
       <c r="J17">
         <v>0.83794199999999996</v>
       </c>
-      <c r="K17" t="s">
+      <c r="K17">
+        <v>-14.91</v>
+      </c>
+      <c r="L17" t="s">
+        <v>59</v>
+      </c>
+      <c r="M17" t="s">
+        <v>25</v>
+      </c>
+      <c r="N17" s="3">
+        <v>0.81712099999999999</v>
+      </c>
+      <c r="O17" s="3">
+        <v>5.0168699999999999</v>
+      </c>
+      <c r="P17" s="3">
+        <v>8.3892799999999994</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>0.68469999999999998</v>
+      </c>
+      <c r="R17" s="3">
+        <v>0.83794199999999996</v>
+      </c>
+      <c r="S17" t="s">
         <v>15</v>
       </c>
-      <c r="M17">
+      <c r="U17">
         <v>-15.03</v>
       </c>
-      <c r="N17">
+      <c r="V17">
         <v>-14.79</v>
       </c>
-      <c r="O17">
+      <c r="W17">
         <f t="shared" si="0"/>
         <v>-14.91</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -1432,21 +1864,45 @@
       <c r="J18">
         <v>0.619807</v>
       </c>
-      <c r="K18" t="s">
+      <c r="K18">
+        <v>-17.399999999999999</v>
+      </c>
+      <c r="L18" t="s">
+        <v>61</v>
+      </c>
+      <c r="M18" t="s">
+        <v>62</v>
+      </c>
+      <c r="N18" s="3">
+        <v>1.04871</v>
+      </c>
+      <c r="O18" s="3">
+        <v>5.1622399999999997</v>
+      </c>
+      <c r="P18" s="3">
+        <v>7.8782199999999998</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>0.65</v>
+      </c>
+      <c r="R18" s="3">
+        <v>0.619807</v>
+      </c>
+      <c r="S18" t="s">
         <v>15</v>
       </c>
-      <c r="M18">
+      <c r="U18">
         <v>-17.45</v>
       </c>
-      <c r="N18">
+      <c r="V18">
         <v>-17.350000000000001</v>
       </c>
-      <c r="O18">
+      <c r="W18">
         <f t="shared" si="0"/>
         <v>-17.399999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -1477,21 +1933,45 @@
       <c r="J19">
         <v>0.83160000000000001</v>
       </c>
-      <c r="K19" t="s">
+      <c r="K19">
+        <v>-15.719999999999999</v>
+      </c>
+      <c r="L19" t="s">
+        <v>64</v>
+      </c>
+      <c r="M19" t="s">
+        <v>25</v>
+      </c>
+      <c r="N19" s="3">
+        <v>0.80146700000000004</v>
+      </c>
+      <c r="O19" s="3">
+        <v>5.40543</v>
+      </c>
+      <c r="P19" s="3">
+        <v>8.3262499999999999</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>0.66649999999999998</v>
+      </c>
+      <c r="R19" s="3">
+        <v>0.83160000000000001</v>
+      </c>
+      <c r="S19" t="s">
         <v>15</v>
       </c>
-      <c r="M19">
+      <c r="U19">
         <v>-15.78</v>
       </c>
-      <c r="N19">
+      <c r="V19">
         <v>-15.66</v>
       </c>
-      <c r="O19">
+      <c r="W19">
         <f t="shared" si="0"/>
         <v>-15.719999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -1522,21 +2002,45 @@
       <c r="J20">
         <v>0.53205999999999998</v>
       </c>
-      <c r="K20" t="s">
+      <c r="K20">
+        <v>-25.515000000000001</v>
+      </c>
+      <c r="L20" t="s">
+        <v>69</v>
+      </c>
+      <c r="M20" t="s">
+        <v>25</v>
+      </c>
+      <c r="N20" s="3">
+        <v>1.1318299999999999</v>
+      </c>
+      <c r="O20" s="3">
+        <v>7.0035699999999999</v>
+      </c>
+      <c r="P20" s="3">
+        <v>7.1830600000000002</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0.60219999999999996</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0.53205999999999998</v>
+      </c>
+      <c r="S20" t="s">
         <v>15</v>
       </c>
-      <c r="M20">
+      <c r="U20">
         <v>-25.6</v>
       </c>
-      <c r="N20">
+      <c r="V20">
         <v>-25.43</v>
       </c>
-      <c r="O20">
+      <c r="W20">
         <f t="shared" si="0"/>
         <v>-25.515000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -1567,21 +2071,45 @@
       <c r="J21">
         <v>0.58620899999999998</v>
       </c>
-      <c r="K21" t="s">
+      <c r="K21">
+        <v>-22.234999999999999</v>
+      </c>
+      <c r="L21" t="s">
+        <v>71</v>
+      </c>
+      <c r="M21" t="s">
+        <v>25</v>
+      </c>
+      <c r="N21" s="3">
+        <v>1.08613</v>
+      </c>
+      <c r="O21" s="3">
+        <v>4.96448</v>
+      </c>
+      <c r="P21" s="3">
+        <v>7.0251999999999999</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>0.63670000000000004</v>
+      </c>
+      <c r="R21" s="3">
+        <v>0.58620899999999998</v>
+      </c>
+      <c r="S21" t="s">
         <v>15</v>
       </c>
-      <c r="M21">
+      <c r="U21">
         <v>-22.29</v>
       </c>
-      <c r="N21">
+      <c r="V21">
         <v>-22.18</v>
       </c>
-      <c r="O21">
+      <c r="W21">
         <f t="shared" si="0"/>
         <v>-22.234999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -1612,21 +2140,45 @@
       <c r="J22">
         <v>0.78891199999999995</v>
       </c>
-      <c r="K22" t="s">
+      <c r="K22">
+        <v>-25.59</v>
+      </c>
+      <c r="L22" t="s">
+        <v>73</v>
+      </c>
+      <c r="M22" t="s">
+        <v>74</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0.86656100000000003</v>
+      </c>
+      <c r="O22" s="3">
+        <v>5.3293600000000003</v>
+      </c>
+      <c r="P22" s="3">
+        <v>5.6953100000000001</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0.68364000000000003</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0.78891199999999995</v>
+      </c>
+      <c r="S22" t="s">
         <v>15</v>
       </c>
-      <c r="M22">
+      <c r="U22">
         <v>-25.65</v>
       </c>
-      <c r="N22">
+      <c r="V22">
         <v>-25.53</v>
       </c>
-      <c r="O22">
+      <c r="W22">
         <f t="shared" si="0"/>
         <v>-25.59</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -1657,21 +2209,45 @@
       <c r="J23">
         <v>0.64227599999999996</v>
       </c>
-      <c r="K23" t="s">
+      <c r="K23">
+        <v>-12.425000000000001</v>
+      </c>
+      <c r="L23" t="s">
+        <v>76</v>
+      </c>
+      <c r="M23" t="s">
+        <v>77</v>
+      </c>
+      <c r="N23" s="3">
+        <v>1.0313300000000001</v>
+      </c>
+      <c r="O23" s="3">
+        <v>5.3329800000000001</v>
+      </c>
+      <c r="P23" s="3">
+        <v>6.2241</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>0.66239999999999999</v>
+      </c>
+      <c r="R23" s="3">
+        <v>0.64227599999999996</v>
+      </c>
+      <c r="S23" t="s">
         <v>15</v>
       </c>
-      <c r="M23">
+      <c r="U23">
         <v>-12.44</v>
       </c>
-      <c r="N23">
+      <c r="V23">
         <v>-12.41</v>
       </c>
-      <c r="O23">
+      <c r="W23">
         <f t="shared" si="0"/>
         <v>-12.425000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>16</v>
       </c>
@@ -1702,21 +2278,45 @@
       <c r="J24">
         <v>0.54868399999999995</v>
       </c>
-      <c r="K24" t="s">
+      <c r="K24">
+        <v>-19.344999999999999</v>
+      </c>
+      <c r="L24" t="s">
+        <v>79</v>
+      </c>
+      <c r="M24" t="s">
+        <v>25</v>
+      </c>
+      <c r="N24" s="3">
+        <v>1.1511199999999999</v>
+      </c>
+      <c r="O24" s="3">
+        <v>4.7761800000000001</v>
+      </c>
+      <c r="P24" s="3">
+        <v>6.7254899999999997</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0.63160000000000005</v>
+      </c>
+      <c r="R24" s="3">
+        <v>0.54868399999999995</v>
+      </c>
+      <c r="S24" t="s">
         <v>15</v>
       </c>
-      <c r="M24">
+      <c r="U24">
         <v>-19.38</v>
       </c>
-      <c r="N24">
+      <c r="V24">
         <v>-19.309999999999999</v>
       </c>
-      <c r="O24">
+      <c r="W24">
         <f t="shared" si="0"/>
         <v>-19.344999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>16</v>
       </c>
@@ -1747,21 +2347,45 @@
       <c r="J25">
         <v>0.54647699999999999</v>
       </c>
-      <c r="K25" t="s">
+      <c r="K25">
+        <v>-23.414999999999999</v>
+      </c>
+      <c r="L25" t="s">
+        <v>81</v>
+      </c>
+      <c r="M25" t="s">
+        <v>25</v>
+      </c>
+      <c r="N25" s="3">
+        <v>1.14845</v>
+      </c>
+      <c r="O25" s="3">
+        <v>4.73691</v>
+      </c>
+      <c r="P25" s="3">
+        <v>6.6952400000000001</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0.62760000000000005</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0.54647699999999999</v>
+      </c>
+      <c r="S25" t="s">
         <v>15</v>
       </c>
-      <c r="M25">
+      <c r="U25">
         <v>-23.46</v>
       </c>
-      <c r="N25">
+      <c r="V25">
         <v>-23.37</v>
       </c>
-      <c r="O25">
+      <c r="W25">
         <f t="shared" si="0"/>
         <v>-23.414999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>16</v>
       </c>
@@ -1793,19 +2417,43 @@
         <v>0.58195200000000002</v>
       </c>
       <c r="K26" t="s">
+        <v>92</v>
+      </c>
+      <c r="L26" t="s">
+        <v>83</v>
+      </c>
+      <c r="M26" t="s">
+        <v>25</v>
+      </c>
+      <c r="N26" s="3">
+        <v>1.0798099999999999</v>
+      </c>
+      <c r="O26" s="3">
+        <v>4.5471500000000002</v>
+      </c>
+      <c r="P26" s="3">
+        <v>6.2913100000000002</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>0.62839999999999996</v>
+      </c>
+      <c r="R26" s="3">
+        <v>0.58195200000000002</v>
+      </c>
+      <c r="S26" t="s">
         <v>15</v>
       </c>
-      <c r="M26" t="s">
+      <c r="U26" t="s">
         <v>92</v>
       </c>
-      <c r="N26" t="s">
+      <c r="V26" t="s">
         <v>92</v>
       </c>
-      <c r="O26" t="s">
+      <c r="W26" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>16</v>
       </c>
@@ -1837,19 +2485,43 @@
         <v>0.55773300000000003</v>
       </c>
       <c r="K27" t="s">
+        <v>92</v>
+      </c>
+      <c r="L27" t="s">
+        <v>85</v>
+      </c>
+      <c r="M27" t="s">
+        <v>31</v>
+      </c>
+      <c r="N27" s="3">
+        <v>1.1311899999999999</v>
+      </c>
+      <c r="O27" s="3">
+        <v>3.5296500000000002</v>
+      </c>
+      <c r="P27" s="3">
+        <v>5.3850499999999997</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>0.63090000000000002</v>
+      </c>
+      <c r="R27" s="3">
+        <v>0.55773300000000003</v>
+      </c>
+      <c r="S27" t="s">
         <v>15</v>
       </c>
-      <c r="M27" t="s">
+      <c r="U27" t="s">
         <v>92</v>
       </c>
-      <c r="N27" t="s">
+      <c r="V27" t="s">
         <v>92</v>
       </c>
-      <c r="O27" t="s">
+      <c r="W27" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>16</v>
       </c>
@@ -1881,19 +2553,43 @@
         <v>0.46045000000000003</v>
       </c>
       <c r="K28" t="s">
+        <v>92</v>
+      </c>
+      <c r="L28" t="s">
+        <v>87</v>
+      </c>
+      <c r="M28" t="s">
+        <v>88</v>
+      </c>
+      <c r="N28" s="3">
+        <v>1.3102400000000001</v>
+      </c>
+      <c r="O28" s="3">
+        <v>4.1586499999999997</v>
+      </c>
+      <c r="P28" s="3">
+        <v>5.5610900000000001</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0.60329999999999995</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0.46045000000000003</v>
+      </c>
+      <c r="S28" t="s">
         <v>15</v>
       </c>
-      <c r="M28" t="s">
+      <c r="U28" t="s">
         <v>92</v>
       </c>
-      <c r="N28" t="s">
+      <c r="V28" t="s">
         <v>92</v>
       </c>
-      <c r="O28" t="s">
+      <c r="W28" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>8</v>
       </c>
@@ -1924,18 +2620,810 @@
       <c r="J29">
         <v>0.61182199999999998</v>
       </c>
-      <c r="K29" t="s">
+      <c r="K29">
+        <v>677.7</v>
+      </c>
+      <c r="L29" t="s">
+        <v>66</v>
+      </c>
+      <c r="M29" t="s">
+        <v>67</v>
+      </c>
+      <c r="N29" s="3">
+        <v>1.0213099999999999</v>
+      </c>
+      <c r="O29" s="3">
+        <v>7.0876900000000003</v>
+      </c>
+      <c r="P29" s="3">
+        <v>7.2475300000000002</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0.62485999999999997</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0.61182199999999998</v>
+      </c>
+      <c r="S29" t="s">
         <v>15</v>
       </c>
-      <c r="M29">
+      <c r="U29">
         <v>677.7</v>
       </c>
-      <c r="N29">
+      <c r="V29">
         <v>677.7</v>
       </c>
-      <c r="O29">
-        <f>M29+(N29-M29)/2</f>
+      <c r="W29">
+        <f>U29+(V29-U29)/2</f>
         <v>677.7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABB5A014-98AD-4900-89A4-4483BCE145F6}">
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0.175207</v>
+      </c>
+      <c r="E2" s="3">
+        <v>15.583130000000001</v>
+      </c>
+      <c r="F2" s="3">
+        <v>22.94791</v>
+      </c>
+      <c r="G2" s="3">
+        <v>0.92854000000000003</v>
+      </c>
+      <c r="H2" s="3">
+        <v>5.2996699999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0.284192</v>
+      </c>
+      <c r="E3" s="3">
+        <v>26.589400000000001</v>
+      </c>
+      <c r="F3" s="3">
+        <v>28.055990000000001</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0.87549999999999994</v>
+      </c>
+      <c r="H3" s="3">
+        <v>3.08066</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0.31795499999999999</v>
+      </c>
+      <c r="E4" s="3">
+        <v>12.16855</v>
+      </c>
+      <c r="F4" s="3">
+        <v>22.459579999999999</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0.86260000000000003</v>
+      </c>
+      <c r="H4" s="3">
+        <v>2.7129599999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1.38141</v>
+      </c>
+      <c r="E5" s="3">
+        <v>11.60045</v>
+      </c>
+      <c r="F5" s="3">
+        <v>12.488670000000001</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0.67900000000000005</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0.49152600000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0.90925500000000004</v>
+      </c>
+      <c r="E6" s="3">
+        <v>14.138949999999999</v>
+      </c>
+      <c r="F6" s="3">
+        <v>15.22231</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0.77549999999999997</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0.85289599999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1.2596700000000001</v>
+      </c>
+      <c r="E7" s="3">
+        <v>8.7666900000000005</v>
+      </c>
+      <c r="F7" s="3">
+        <v>9.2239699999999996</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0.61970000000000003</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0.49195499999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0.89958000000000005</v>
+      </c>
+      <c r="E8" s="3">
+        <v>7.2826300000000002</v>
+      </c>
+      <c r="F8" s="3">
+        <v>13.220230000000001</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0.72829999999999995</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0.80959999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1.56151</v>
+      </c>
+      <c r="E9" s="3">
+        <v>6.1713699999999996</v>
+      </c>
+      <c r="F9" s="3">
+        <v>11.808210000000001</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0.70289999999999997</v>
+      </c>
+      <c r="H9" s="3">
+        <v>0.45014199999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0.88899499999999998</v>
+      </c>
+      <c r="E10" s="3">
+        <v>8.2379499999999997</v>
+      </c>
+      <c r="F10" s="3">
+        <v>9.7940900000000006</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0.67300000000000004</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0.75703500000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0.833314</v>
+      </c>
+      <c r="E11" s="3">
+        <v>8.5407899999999994</v>
+      </c>
+      <c r="F11" s="3">
+        <v>9.9702599999999997</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0.70909999999999995</v>
+      </c>
+      <c r="H11" s="3">
+        <v>0.850939</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0.70806999999999998</v>
+      </c>
+      <c r="E12" s="3">
+        <v>9.5747199999999992</v>
+      </c>
+      <c r="F12" s="3">
+        <v>12.54203</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0.72019999999999995</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1.0171300000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0.70865800000000001</v>
+      </c>
+      <c r="E13" s="3">
+        <v>6.1979199999999999</v>
+      </c>
+      <c r="F13" s="3">
+        <v>11.543760000000001</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0.7329</v>
+      </c>
+      <c r="H13" s="3">
+        <v>1.0342100000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0.63210100000000002</v>
+      </c>
+      <c r="E14" s="3">
+        <v>6.5133400000000004</v>
+      </c>
+      <c r="F14" s="3">
+        <v>10.863440000000001</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0.71786000000000005</v>
+      </c>
+      <c r="H14" s="3">
+        <v>1.13567</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0.76535500000000001</v>
+      </c>
+      <c r="E15" s="3">
+        <v>10.29832</v>
+      </c>
+      <c r="F15" s="3">
+        <v>10.43276</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0.66347999999999996</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0.86689099999999997</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0.64188900000000004</v>
+      </c>
+      <c r="E16" s="3">
+        <v>4.1592000000000002</v>
+      </c>
+      <c r="F16" s="3">
+        <v>9.4749199999999991</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0.73499999999999999</v>
+      </c>
+      <c r="H16" s="3">
+        <v>1.14506</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0.81712099999999999</v>
+      </c>
+      <c r="E17" s="3">
+        <v>5.0168699999999999</v>
+      </c>
+      <c r="F17" s="3">
+        <v>8.3892799999999994</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0.68469999999999998</v>
+      </c>
+      <c r="H17" s="3">
+        <v>0.83794199999999996</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" s="3">
+        <v>1.04871</v>
+      </c>
+      <c r="E18" s="3">
+        <v>5.1622399999999997</v>
+      </c>
+      <c r="F18" s="3">
+        <v>7.8782199999999998</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0.65</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0.619807</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B19" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" s="3">
+        <v>0.80146700000000004</v>
+      </c>
+      <c r="E19" s="3">
+        <v>5.40543</v>
+      </c>
+      <c r="F19" s="3">
+        <v>8.3262499999999999</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0.66649999999999998</v>
+      </c>
+      <c r="H19" s="3">
+        <v>0.83160000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="3">
+        <v>1.1318299999999999</v>
+      </c>
+      <c r="E20" s="3">
+        <v>7.0035699999999999</v>
+      </c>
+      <c r="F20" s="3">
+        <v>7.1830600000000002</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0.60219999999999996</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0.53205999999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21" s="3">
+        <v>1.08613</v>
+      </c>
+      <c r="E21" s="3">
+        <v>4.96448</v>
+      </c>
+      <c r="F21" s="3">
+        <v>7.0251999999999999</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0.63670000000000004</v>
+      </c>
+      <c r="H21" s="3">
+        <v>0.58620899999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" t="s">
+        <v>74</v>
+      </c>
+      <c r="D22" s="3">
+        <v>0.86656100000000003</v>
+      </c>
+      <c r="E22" s="3">
+        <v>5.3293600000000003</v>
+      </c>
+      <c r="F22" s="3">
+        <v>5.6953100000000001</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0.68364000000000003</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0.78891199999999995</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23" s="3">
+        <v>1.0313300000000001</v>
+      </c>
+      <c r="E23" s="3">
+        <v>5.3329800000000001</v>
+      </c>
+      <c r="F23" s="3">
+        <v>6.2241</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0.66239999999999999</v>
+      </c>
+      <c r="H23" s="3">
+        <v>0.64227599999999996</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>78</v>
+      </c>
+      <c r="B24" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24" s="3">
+        <v>1.1511199999999999</v>
+      </c>
+      <c r="E24" s="3">
+        <v>4.7761800000000001</v>
+      </c>
+      <c r="F24" s="3">
+        <v>6.7254899999999997</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0.63160000000000005</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0.54868399999999995</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25" s="3">
+        <v>1.14845</v>
+      </c>
+      <c r="E25" s="3">
+        <v>4.73691</v>
+      </c>
+      <c r="F25" s="3">
+        <v>6.6952400000000001</v>
+      </c>
+      <c r="G25" s="3">
+        <v>0.62760000000000005</v>
+      </c>
+      <c r="H25" s="3">
+        <v>0.54647699999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="3">
+        <v>1.0798099999999999</v>
+      </c>
+      <c r="E26" s="3">
+        <v>4.5471500000000002</v>
+      </c>
+      <c r="F26" s="3">
+        <v>6.2913100000000002</v>
+      </c>
+      <c r="G26" s="3">
+        <v>0.62839999999999996</v>
+      </c>
+      <c r="H26" s="3">
+        <v>0.58195200000000002</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>84</v>
+      </c>
+      <c r="B27" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27" s="3">
+        <v>1.1311899999999999</v>
+      </c>
+      <c r="E27" s="3">
+        <v>3.5296500000000002</v>
+      </c>
+      <c r="F27" s="3">
+        <v>5.3850499999999997</v>
+      </c>
+      <c r="G27" s="3">
+        <v>0.63090000000000002</v>
+      </c>
+      <c r="H27" s="3">
+        <v>0.55773300000000003</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>86</v>
+      </c>
+      <c r="B28" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" t="s">
+        <v>88</v>
+      </c>
+      <c r="D28" s="3">
+        <v>1.3102400000000001</v>
+      </c>
+      <c r="E28" s="3">
+        <v>4.1586499999999997</v>
+      </c>
+      <c r="F28" s="3">
+        <v>5.5610900000000001</v>
+      </c>
+      <c r="G28" s="3">
+        <v>0.60329999999999995</v>
+      </c>
+      <c r="H28" s="3">
+        <v>0.46045000000000003</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>65</v>
+      </c>
+      <c r="B29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29" s="3">
+        <v>1.0213099999999999</v>
+      </c>
+      <c r="E29" s="3">
+        <v>7.0876900000000003</v>
+      </c>
+      <c r="F29" s="3">
+        <v>7.2475300000000002</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0.62485999999999997</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0.61182199999999998</v>
       </c>
     </row>
   </sheetData>
